--- a/workpapers/logical-access-workpaper.xlsx
+++ b/workpapers/logical-access-workpaper.xlsx
@@ -27,38 +27,38 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$J$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$J$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AC-01'!$A$12:$D$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'AC-01'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AC-02'!$A$12:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'AC-02'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'AC-03'!$A$12:$D$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'AC-03'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AC-04'!$A$12:$D$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'AC-04'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AC-05'!$A$12:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'AC-05'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AC-06'!$A$12:$D$40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'AC-06'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'AC-07'!$A$12:$D$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'AC-07'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AC-08'!$A$12:$D$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'AC-08'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'AC-09'!$A$12:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'AC-09'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AC-10'!$A$12:$D$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'AC-10'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AC-11'!$A$12:$D$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'AC-11'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'AC-12'!$A$12:$D$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'AC-12'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'AC-13'!$A$12:$D$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'AC-13'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'AC-14'!$A$12:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'AC-14'!$12:$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AC-01'!$A$14:$D$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'AC-01'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AC-02'!$A$14:$D$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'AC-02'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'AC-03'!$A$14:$D$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'AC-03'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AC-04'!$A$14:$D$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'AC-04'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AC-05'!$A$14:$D$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'AC-05'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AC-06'!$A$14:$D$42</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'AC-06'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'AC-07'!$A$14:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'AC-07'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AC-08'!$A$14:$D$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'AC-08'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'AC-09'!$A$14:$D$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'AC-09'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AC-10'!$A$14:$D$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'AC-10'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AC-11'!$A$14:$D$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'AC-11'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'AC-12'!$A$14:$D$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'AC-12'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'AC-13'!$A$14:$D$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'AC-13'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'AC-14'!$A$14:$D$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'AC-14'!$14:$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Evidence'!$A$1:$C$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="17">'Evidence'!$1:$1</definedName>
   </definedNames>
@@ -699,7 +699,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 03:15 UTC</t>
+          <t>2026-10-27 03:41 UTC</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -768,184 +768,164 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>A.5.17 Authentication information; A.8.5 Secure authentication</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Passwords are hard to guess and accounts cannot be attacked by repeated guessing.</t>
+          <t>5.2 Use unique passwords</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Read the live domain password settings and compare each with the policy.</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The domain password policy (one configuration)</t>
+          <t>Passwords are hard to guess and accounts cannot be attacked by repeated guessing.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>Read the live domain password settings and compare each with the policy.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Design deficiency (2 exceptions in 6 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>The domain password policy (one configuration)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Design deficiency (2 exceptions in 6 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Minimum password length</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Configured 8; policy requires &gt;= 12.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Password complexity</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Configured on; policy requires on.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Password history length</t>
+          <t>Minimum password length</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Configured 24; policy requires &gt;= 24.</t>
+          <t>Configured 8; policy requires &gt;= 12.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Maximum password age (days)</t>
+          <t>Password complexity</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -955,64 +935,110 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Configured 42; policy requires 1 to 90.</t>
+          <t>Configured on; policy requires on.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Account lockout threshold (attempts)</t>
+          <t>Password history length</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Configured 0; policy requires 1 to 5. A threshold of 0 means accounts never lock.</t>
+          <t>Configured 24; policy requires &gt;= 24.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Maximum password age (days)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Configured 42; policy requires 1 to 90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Account lockout threshold (attempts)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Configured 0; policy requires 1 to 5. A threshold of 0 means accounts never lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>Account lockout duration (mins)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Configured 30; policy requires &gt;= 15. Has no effect while lockout is disabled.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D18"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D20"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -1035,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1066,207 +1092,233 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.17 Authentication information</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Every person's password is changed regularly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>5.2 Use unique passwords; 5.5 Inventory of service accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>List every enabled account whose password is set never to expire. Each must be a service account with an approved, in date entry in the exception register.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All enabled accounts with non-expiring passwords</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Every person's password is changed regularly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>List every enabled account whose password is set never to expire. Each must be a service account with an approved, in date entry in the exception register.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (2 exceptions in 4 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All enabled accounts with non-expiring passwords</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (2 exceptions in 4 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>finance.shared</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Generic account; no approved exception.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>sarah.mitchell</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Personal account; no approved exception.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>svc-backup</t>
+          <t>finance.shared</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Generic</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Approved exception EX-2024-02 by james.carter, review due 2027-01-15.</t>
+          <t>Generic account; no approved exception.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>sarah.mitchell</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Personal account; no approved exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>svc-backup</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Approved exception EX-2024-02 by james.carter, review due 2027-01-15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>svc-financeapp</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Approved exception EX-2024-01 by james.carter, review due 2027-01-15.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D16"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D18"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -1289,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1320,141 +1372,167 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.16 Identity management</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Every action can be traced to one person.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>5.1 Inventory of accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>List every enabled account that is not personal, administrator, service or built in, and confirm its purpose from its description.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All enabled generic accounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Every action can be traced to one person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>List every enabled account that is not personal, administrator, service or built in, and confirm its purpose from its description.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (1 exception in 1 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All enabled generic accounts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (1 exception in 1 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>finance.shared</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Shared finance team login</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Shared login used by more than one person. Member of Finance-Payments-Initiators, GG-Finance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D13"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D15"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -1477,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1508,162 +1586,142 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A.8.2 Privileged access rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CIS Controls v8.1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>5.4 Dedicated administrator accounts; 5.5 Inventory of service accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Test type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Control objective</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Full control of the domain is held only by people who need it, through separate accounts that are not used for everyday work.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Test procedure</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>List every member of Domain Admins. Each must be a separate adm. account with an approved request, or the built in Administrator account. Day to day accounts and service accounts are exceptions unless an approved exception exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>All members of Domain Admins</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Whole population</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (2 exceptions in 5 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All members of Domain Admins</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (2 exceptions in 5 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Built in</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Built in break glass account. Its use should be monitored; see observation O1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>adm.akhan</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Separate admin account; REQ-2022-011 approved by james.carter.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>adm.jcarter</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Built in</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1673,64 +1731,110 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Separate admin account; REQ-2019-024 approved by Chief Executive.</t>
+          <t>Built in break glass account. Its use should be monitored; see observation O1.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>liam.brooks</t>
+          <t>adm.akhan</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Everyday personal account with full domain admin rights and no approved request. Approved access: REQ-2023-047 Helpdesk.</t>
+          <t>Separate admin account; REQ-2022-011 approved by james.carter.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>adm.jcarter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Separate admin account; REQ-2019-024 approved by Chief Executive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>liam.brooks</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Everyday personal account with full domain admin rights and no approved request. Approved access: REQ-2023-047 Helpdesk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>svc-backup</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Service account in Domain Admins with no exception recorded under clause 5.3 (its exception covers only clause 4.3).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D17"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D19"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -1753,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1784,157 +1888,137 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.3 Segregation of duties</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>A single person cannot make and approve a fraudulent payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>6.8 Role based access</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Compare the members of Finance-Payments-Initiators with the members of Finance-Payments-Approvers. Anyone in both is an exception.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All members of either payments group</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>A single person cannot make and approve a fraudulent payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>Compare the members of Finance-Payments-Initiators with the members of Finance-Payments-Approvers. Anyone in both is an exception.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (1 exception in 7 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All members of either payments group</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (1 exception in 7 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>chloe.evans</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Initiator</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>One role only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>daniel.hughes</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Initiator</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>One role only.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>emma.wilson</t>
+          <t>chloe.evans</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1956,7 +2040,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>finance.shared</t>
+          <t>daniel.hughes</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1978,12 +2062,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>mark.taylor</t>
+          <t>emma.wilson</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Approver</t>
+          <t>Initiator</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2000,12 +2084,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>olivia.bennett</t>
+          <t>finance.shared</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Approver</t>
+          <t>Initiator</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -2022,35 +2106,81 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>mark.taylor</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Approver</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>One role only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>olivia.bennett</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Approver</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>One role only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>priya.shah</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Initiator and Approver</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Holds both conflicting roles.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D19"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D21"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -2073,7 +2203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2104,162 +2234,142 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.3 Segregation of duties; A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Access is always checked by someone other than the person receiving it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>6.1 Access granting process</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Inspect every access request. Any request approved by the person it gives access to is an exception.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All 18 access requests in the access request log</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Access is always checked by someone other than the person receiving it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>Inspect every access request. Any request approved by the person it gives access to is an exception.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (1 exception in 18 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All 18 access requests in the access request log</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (1 exception in 18 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>REQ-2019-014</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>olivia.bennett: Finance-Payments-Approvers</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Approved by Chief Executive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>REQ-2019-022</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>james.carter: IT-Server-Admins</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Approved by Chief Executive.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>REQ-2019-023</t>
+          <t>REQ-2019-014</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>james.carter: Change-Approvers</t>
+          <t>olivia.bennett: Finance-Payments-Approvers</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2276,12 +2386,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>REQ-2019-024</t>
+          <t>REQ-2019-022</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>adm.jcarter: Domain Admins</t>
+          <t>james.carter: IT-Server-Admins</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2298,12 +2408,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>REQ-2020-006</t>
+          <t>REQ-2019-023</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>mark.taylor: Finance-Payments-Approvers</t>
+          <t>james.carter: Change-Approvers</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2313,19 +2423,19 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Approved by olivia.bennett.</t>
+          <t>Approved by Chief Executive.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>REQ-2021-031</t>
+          <t>REQ-2019-024</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>priya.shah: Finance-Payments-Initiators</t>
+          <t>adm.jcarter: Domain Admins</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -2335,19 +2445,19 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Approved by olivia.bennett.</t>
+          <t>Approved by Chief Executive.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-009</t>
+          <t>REQ-2020-006</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>aisha.khan: IT-Server-Admins</t>
+          <t>mark.taylor: Finance-Payments-Approvers</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -2357,19 +2467,19 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Approved by james.carter.</t>
+          <t>Approved by olivia.bennett.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-010</t>
+          <t>REQ-2021-031</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>aisha.khan: Change-Deployers</t>
+          <t>priya.shah: Finance-Payments-Initiators</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -2379,19 +2489,19 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Approved by james.carter.</t>
+          <t>Approved by olivia.bennett.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-011</t>
+          <t>REQ-2022-009</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>adm.akhan: Domain Admins</t>
+          <t>aisha.khan: IT-Server-Admins</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -2408,12 +2518,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-035</t>
+          <t>REQ-2022-010</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>emma.wilson: Finance-Payments-Initiators</t>
+          <t>aisha.khan: Change-Deployers</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -2423,19 +2533,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Approved by olivia.bennett.</t>
+          <t>Approved by james.carter.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-052</t>
+          <t>REQ-2022-011</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ryan.patel: Change-Deployers</t>
+          <t>adm.akhan: Domain Admins</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -2452,12 +2562,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>REQ-2023-002</t>
+          <t>REQ-2022-035</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>daniel.hughes: Finance-Payments-Initiators</t>
+          <t>emma.wilson: Finance-Payments-Initiators</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -2474,12 +2584,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>REQ-2023-047</t>
+          <t>REQ-2022-052</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>liam.brooks: Helpdesk</t>
+          <t>ryan.patel: Change-Deployers</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -2496,12 +2606,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>REQ-2024-019</t>
+          <t>REQ-2023-002</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>chloe.evans: Finance-Payments-Initiators</t>
+          <t>daniel.hughes: Finance-Payments-Initiators</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -2518,34 +2628,34 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>REQ-2025-118</t>
+          <t>REQ-2023-047</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>priya.shah: Finance-Payments-Approvers</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>liam.brooks: Helpdesk</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Requested and approved by priya.shah, for their own account.</t>
+          <t>Approved by james.carter.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>REQ-2026-061</t>
+          <t>REQ-2024-019</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>jack.lewis: GG-Sales</t>
+          <t>chloe.evans: Finance-Payments-Initiators</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2555,64 +2665,110 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Approved by ben.foster.</t>
+          <t>Approved by olivia.bennett.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>REQ-2026-072</t>
+          <t>REQ-2025-118</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ava.king: GG-Operations</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>priya.shah: Finance-Payments-Approvers</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Approved by noah.green.</t>
+          <t>Requested and approved by priya.shah, for their own account.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>REQ-2026-061</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>jack.lewis: GG-Sales</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Approved by ben.foster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>REQ-2026-072</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>ava.king: GG-Operations</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Approved by noah.green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>REQ-2026-084</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>emma.wilson: GG-Sales</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Approved by ben.foster.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D30"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D32"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -2635,7 +2791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2666,223 +2822,203 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.18 Access rights; A.8.2 Privileged access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>CIS Controls v8.1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>6.1 Access granting process; 6.8 Role based access</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Test type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Operating effectiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>Control objective</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Nobody holds powerful access that the business did not approve.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Test procedure</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>For every member of each sensitive group, find an approved access request for that group. Requests approved by the person themselves are dealt with in AC-12.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>All members of: Domain Admins, IT-Server-Admins, Finance-Payments-Initiators, Finance-Payments-Approvers, Change-Approvers, Change-Deployers</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Whole population</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (3 exceptions in 17 tested)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (3 exceptions in 17 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F2, F3</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Domain Admins: Administrator</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Built in</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Built in account, created with the domain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Domain Admins: adm.akhan</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>REQ-2022-011 approved by james.carter on 2022-02-07.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Domain Admins: adm.jcarter</t>
+          <t>Domain Admins: Administrator</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Built in</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>REQ-2019-024 approved by Chief Executive on 2019-05-13.</t>
+          <t>Built in account, created with the domain.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Domain Admins: liam.brooks</t>
+          <t>Domain Admins: adm.akhan</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>No approved request.</t>
+          <t>REQ-2022-011 approved by james.carter on 2022-02-07.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Domain Admins: svc-backup</t>
+          <t>Domain Admins: adm.jcarter</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>No approved request.</t>
+          <t>REQ-2019-024 approved by Chief Executive on 2019-05-13.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>IT-Server-Admins: aisha.khan</t>
+          <t>Domain Admins: liam.brooks</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -2890,43 +3026,43 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-009 approved by james.carter on 2022-02-04.</t>
+          <t>No approved request.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IT-Server-Admins: james.carter</t>
+          <t>Domain Admins: svc-backup</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>REQ-2019-022 approved by Chief Executive on 2019-05-10.</t>
+          <t>No approved request.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Initiators: chloe.evans</t>
+          <t>IT-Server-Admins: aisha.khan</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2941,14 +3077,14 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>REQ-2024-019 approved by olivia.bennett on 2024-05-16.</t>
+          <t>REQ-2022-009 approved by james.carter on 2022-02-04.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Initiators: daniel.hughes</t>
+          <t>IT-Server-Admins: james.carter</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2963,14 +3099,14 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>REQ-2023-002 approved by olivia.bennett on 2023-01-06.</t>
+          <t>REQ-2019-022 approved by Chief Executive on 2019-05-10.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Initiators: emma.wilson</t>
+          <t>Finance-Payments-Initiators: chloe.evans</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2985,36 +3121,36 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-035 approved by olivia.bennett on 2022-06-02.</t>
+          <t>REQ-2024-019 approved by olivia.bennett on 2024-05-16.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Initiators: finance.shared</t>
+          <t>Finance-Payments-Initiators: daniel.hughes</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>No approved request.</t>
+          <t>REQ-2023-002 approved by olivia.bennett on 2023-01-06.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Initiators: priya.shah</t>
+          <t>Finance-Payments-Initiators: emma.wilson</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3029,36 +3165,36 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>REQ-2021-031 approved by olivia.bennett on 2021-06-11.</t>
+          <t>REQ-2022-035 approved by olivia.bennett on 2022-06-02.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Approvers: mark.taylor</t>
+          <t>Finance-Payments-Initiators: finance.shared</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Generic</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>REQ-2020-006 approved by olivia.bennett on 2020-01-31.</t>
+          <t>No approved request.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Approvers: olivia.bennett</t>
+          <t>Finance-Payments-Initiators: priya.shah</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -3073,14 +3209,14 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>REQ-2019-014 approved by Chief Executive on 2019-03-01.</t>
+          <t>REQ-2021-031 approved by olivia.bennett on 2021-06-11.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Finance-Payments-Approvers: priya.shah</t>
+          <t>Finance-Payments-Approvers: mark.taylor</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -3095,14 +3231,14 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>REQ-2025-118 approved by priya.shah on 2025-11-03.</t>
+          <t>REQ-2020-006 approved by olivia.bennett on 2020-01-31.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Change-Approvers: james.carter</t>
+          <t>Finance-Payments-Approvers: olivia.bennett</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -3117,14 +3253,14 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>REQ-2019-023 approved by Chief Executive on 2019-05-10.</t>
+          <t>REQ-2019-014 approved by Chief Executive on 2019-03-01.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Change-Deployers: aisha.khan</t>
+          <t>Finance-Payments-Approvers: priya.shah</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3139,42 +3275,88 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>REQ-2022-010 approved by james.carter on 2022-02-04.</t>
+          <t>REQ-2025-118 approved by priya.shah on 2025-11-03.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Change-Approvers: james.carter</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>REQ-2019-023 approved by Chief Executive on 2019-05-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Change-Deployers: aisha.khan</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>REQ-2022-010 approved by james.carter on 2022-02-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Change-Deployers: ryan.patel</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>REQ-2022-052 approved by james.carter on 2022-09-09.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D30"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D32"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -3197,7 +3379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3228,141 +3410,167 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Access that is no longer needed is found and removed even when other controls miss it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>6.8 Role based access (recurring access reviews)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Request the signed off Q3 2026 review of Domain Admins, IT-Server-Admins and the two payments groups, and re-perform a sample of the review's conclusions.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The Q3 2026 quarterly access review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Access that is no longer needed is found and removed even when other controls miss it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>Request the signed off Q3 2026 review of Domain Admins, IT-Server-Admins and the two payments groups, and re-perform a sample of the review's conclusions.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (1 exception in 1 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>The Q3 2026 quarterly access review</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (1 exception in 1 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Q3 2026 access review</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Requested from the Head of IT</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>No evidence of a review was provided. Several exceptions found in this testing (AC-01, AC-02, AC-10, AC-11) would have been caught by an effective review.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D13"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D15"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -3536,17 +3744,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3590,6 +3800,16 @@
           <t>Findings</t>
         </is>
       </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>CIS Controls v8.1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -3628,6 +3848,16 @@
           <t>F1</t>
         </is>
       </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>6.2 Access revoking process</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -3666,6 +3896,16 @@
           <t>F4</t>
         </is>
       </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>6.2 Access revoking process; 6.8 Role based access</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3700,6 +3940,16 @@
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>6.1 Access granting process</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3738,6 +3988,16 @@
           <t>F1, F5</t>
         </is>
       </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>A.5.16 Identity management; A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>5.1 Inventory of accounts; 6.2 Access revoking process</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -3776,6 +4036,16 @@
           <t>F5</t>
         </is>
       </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>6.2 Access revoking process</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -3814,6 +4084,16 @@
           <t>F5, F9</t>
         </is>
       </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>5.3 Disable dormant accounts</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -3852,6 +4132,16 @@
           <t>F6</t>
         </is>
       </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>A.5.17 Authentication information; A.8.5 Secure authentication</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>5.2 Use unique passwords</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3890,6 +4180,16 @@
           <t>F7</t>
         </is>
       </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>A.5.17 Authentication information</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>5.2 Use unique passwords; 5.5 Inventory of service accounts</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3928,6 +4228,16 @@
           <t>F3</t>
         </is>
       </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>A.5.16 Identity management</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>5.1 Inventory of accounts</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3966,6 +4276,16 @@
           <t>F2</t>
         </is>
       </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>A.8.2 Privileged access rights</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>5.4 Dedicated administrator accounts; 5.5 Inventory of service accounts</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4004,6 +4324,16 @@
           <t>F8</t>
         </is>
       </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>A.5.3 Segregation of duties</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>6.8 Role based access</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4042,6 +4372,16 @@
           <t>F8</t>
         </is>
       </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>A.5.3 Segregation of duties; A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>6.1 Access granting process</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4080,6 +4420,16 @@
           <t>F2, F3</t>
         </is>
       </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights; A.8.2 Privileged access rights</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>6.1 Access granting process; 6.8 Role based access</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4118,9 +4468,19 @@
           <t>F10</t>
         </is>
       </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>6.8 Role based access (recurring access reviews)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:J15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -4656,7 +5016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4687,185 +5047,211 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Former employees cannot use their access after they leave.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>6.2 Access revoking process</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>From the HR extract, select every employee with a leaving date in the audit period. Find each one's account by employee ID. Check the account is disabled, removed from all groups and moved to the Leavers area, and compare any last logon date with the leaving date. Deadline: 1 working day after the leaving date.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All employees who left between 1 July and 30 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Former employees cannot use their access after they leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>From the HR extract, select every employee with a leaving date in the audit period. Find each one's account by employee ID. Check the account is disabled, removed from all groups and moved to the Leavers area, and compare any last logon date with the leaving date. Deadline: 1 working day after the leaving date.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (1 exception in 3 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All employees who left between 1 July and 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (1 exception in 3 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>mark.taylor: Mark Taylor (NW1004)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Left 2026-08-29; deadline 2026-09-01</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Account still enabled at 2026-10-27, 56 days after the 2026-09-01 deadline; still a member of Finance-Payments-Approvers, GG-Finance; not moved to Leavers (located in Finance/Staff/Northwind); account signed in on 2026-10-27, after the leaving date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>oliver.scott: Oliver Scott (NW1014)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Left 2026-07-31; deadline 2026-08-03</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Disabled, no group memberships, in Leavers.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>mark.taylor: Mark Taylor (NW1004)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Left 2026-08-29; deadline 2026-09-01</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Account still enabled at 2026-10-27, 56 days after the 2026-09-01 deadline; still a member of Finance-Payments-Approvers, GG-Finance; not moved to Leavers (located in Finance/Staff/Northwind); account signed in on 2026-10-27, after the leaving date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>oliver.scott: Oliver Scott (NW1014)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Left 2026-07-31; deadline 2026-08-03</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Disabled, no group memberships, in Leavers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>isla.wright: Isla Wright (NW1021)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Left 2026-09-19; deadline 2026-09-21</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Disabled, no group memberships, in Leavers.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D15"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D17"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -4888,7 +5274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4919,141 +5305,167 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>People do not keep access from a previous role that they no longer need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+          <t>6.2 Access revoking process; 6.8 Role based access</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>From the HR extract, select every employee who transferred department in the audit period. Compare their current group memberships with their new department. Any group belonging to the previous department still held 5 working days after the transfer is an exception.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All transfers between 1 July and 30 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>People do not keep access from a previous role that they no longer need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>From the HR extract, select every employee who transferred department in the audit period. Compare their current group memberships with their new department. Any group belonging to the previous department still held 5 working days after the transfer is an exception.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (1 exception in 1 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All transfers between 1 July and 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (1 exception in 1 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>emma.wilson</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Finance to Sales on 2026-09-14; deadline 2026-09-21</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Still holds Finance-Payments-Initiators, GG-Finance at 2026-10-27, 36 days after the deadline.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D13"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D15"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -5076,7 +5488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5107,163 +5519,189 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Access is only given when the business has asked for it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+          <t>6.1 Access granting process</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>From the HR extract, select every employee who started in the audit period. For each, find the access request, and check it was approved by the line manager recorded in HR, on or before the start date, and that the groups granted match the request.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All starters between 1 July and 30 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Access is only given when the business has asked for it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>From the HR extract, select every employee who started in the audit period. For each, find the access request, and check it was approved by the line manager recorded in HR, on or before the start date, and that the groups granted match the request.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Effective (no exceptions)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All starters between 1 July and 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Effective (no exceptions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>jack.lewis</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Started 2026-07-20; line manager ben.foster</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>GG-Sales: REQ-2026-061 approved by ben.foster on 2026-07-15</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>ava.king</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Started 2026-08-03; line manager noah.green</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>GG-Operations: REQ-2026-072 approved by noah.green on 2026-07-30</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D14"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D16"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -5286,7 +5724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5317,162 +5755,142 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.16 Identity management; A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No active account exists for someone who no longer works for the company.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>5.1 Inventory of accounts; 6.2 Access revoking process</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>List every enabled personal account in the directory. Match each one by employee or contractor ID to the HR extract and contractor list. An account with no match, or whose match has left or whose contract has ended, is an exception. Generic, administrator, service and built in accounts are tested in AC-08 to AC-10.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All enabled personal accounts at the extraction date</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>No active account exists for someone who no longer works for the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>List every enabled personal account in the directory. Match each one by employee or contractor ID to the HR extract and contractor list. An account with no match, or whose match has left or whose contract has ended, is an exception. Generic, administrator, service and built in accounts are tested in AC-08 to AC-10.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (2 exceptions in 22 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All enabled personal accounts at the extraction date</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (2 exceptions in 22 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F1, F5</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>aisha.khan</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>NW1009</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Matches active employee Aisha Khan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ava.king</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>NW1027</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Matches active employee Ava King.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ben.foster</t>
+          <t>aisha.khan</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>NW1005</t>
+          <t>NW1009</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -5482,19 +5900,19 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Ben Foster.</t>
+          <t>Matches active employee Aisha Khan.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>chloe.evans</t>
+          <t>ava.king</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>NW1022</t>
+          <t>NW1027</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -5504,19 +5922,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Chloe Evans.</t>
+          <t>Matches active employee Ava King.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>daniel.hughes</t>
+          <t>ben.foster</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>NW1015</t>
+          <t>NW1005</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -5526,19 +5944,19 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Daniel Hughes.</t>
+          <t>Matches active employee Ben Foster.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>emma.wilson</t>
+          <t>chloe.evans</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>NW1011</t>
+          <t>NW1022</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -5548,19 +5966,19 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Emma Wilson.</t>
+          <t>Matches active employee Chloe Evans.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ethan.young</t>
+          <t>daniel.hughes</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>NW1020</t>
+          <t>NW1015</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -5570,19 +5988,19 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Ethan Young.</t>
+          <t>Matches active employee Daniel Hughes.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>grace.thompson</t>
+          <t>emma.wilson</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>NW1003</t>
+          <t>NW1011</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -5592,19 +6010,19 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Grace Thompson.</t>
+          <t>Matches active employee Emma Wilson.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>harry.walker</t>
+          <t>ethan.young</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NW1019</t>
+          <t>NW1020</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -5614,19 +6032,19 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Harry Walker.</t>
+          <t>Matches active employee Ethan Young.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>jack.lewis</t>
+          <t>grace.thompson</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>NW1026</t>
+          <t>NW1003</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -5636,19 +6054,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Jack Lewis.</t>
+          <t>Matches active employee Grace Thompson.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>james.carter</t>
+          <t>harry.walker</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NW1002</t>
+          <t>NW1019</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -5658,41 +6076,41 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee James Carter.</t>
+          <t>Matches active employee Harry Walker.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>leo.martin</t>
+          <t>jack.lewis</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>C-0042</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>NW1026</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Contract with DevPartners Ltd ended on 2026-06-30 but the account is enabled.</t>
+          <t>Matches active employee Jack Lewis.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>liam.brooks</t>
+          <t>james.carter</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>NW1018</t>
+          <t>NW1002</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -5702,63 +6120,63 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Liam Brooks.</t>
+          <t>Matches active employee James Carter.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>lucy.hall</t>
+          <t>leo.martin</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>NW1013</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>C-0042</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Lucy Hall.</t>
+          <t>Contract with DevPartners Ltd ended on 2026-06-30 but the account is enabled.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>mark.taylor</t>
+          <t>liam.brooks</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>NW1004</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+          <t>NW1018</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Employee left on 2026-08-29 but the account is enabled.</t>
+          <t>Matches active employee Liam Brooks.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>mia.roberts</t>
+          <t>lucy.hall</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>NW1024</t>
+          <t>NW1013</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5768,41 +6186,41 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Mia Roberts.</t>
+          <t>Matches active employee Lucy Hall.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>noah.green</t>
+          <t>mark.taylor</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>NW1006</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>NW1004</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Noah Green.</t>
+          <t>Employee left on 2026-08-29 but the account is enabled.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>olivia.bennett</t>
+          <t>mia.roberts</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>NW1001</t>
+          <t>NW1024</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -5812,19 +6230,19 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Olivia Bennett.</t>
+          <t>Matches active employee Mia Roberts.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>priya.shah</t>
+          <t>noah.green</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>NW1007</t>
+          <t>NW1006</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -5834,19 +6252,19 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Priya Shah.</t>
+          <t>Matches active employee Noah Green.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ryan.patel</t>
+          <t>olivia.bennett</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>NW1012</t>
+          <t>NW1001</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -5856,19 +6274,19 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Ryan Patel.</t>
+          <t>Matches active employee Olivia Bennett.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>sarah.mitchell</t>
+          <t>priya.shah</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>NW1010</t>
+          <t>NW1007</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -5878,42 +6296,88 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Matches active employee Sarah Mitchell.</t>
+          <t>Matches active employee Priya Shah.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>ryan.patel</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>NW1012</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Matches active employee Ryan Patel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>sarah.mitchell</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>NW1010</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Matches active employee Sarah Mitchell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>sophie.turner</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>NW1016</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Matches active employee Sophie Turner.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D34"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D36"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -5936,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5967,141 +6431,167 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A.5.18 Access rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CIS Controls v8.1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>6.2 Access revoking process</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Test type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Control objective</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>A contractor's access stops automatically when their contract ends, even if nobody remembers to remove it.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Test procedure</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>For every contractor on the contractor list, find their account and check its expiry date is set to the contract end date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>All contractors on the contractor list</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Whole population</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Design deficiency (1 exception in 1 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All contractors on the contractor list</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Design deficiency (1 exception in 1 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>leo.martin</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Contract ended 2026-06-30</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Account expiry: Never. No expiry was set, so the account stayed usable after the contract ended.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D13"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D15"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -6124,7 +6614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6155,162 +6645,142 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Test type</t>
+          <t>ISO/IEC 27001:2022</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Operating effectiveness</t>
+          <t>A.5.18 Access rights</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Control objective</t>
+          <t>CIS Controls v8.1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Accounts nobody uses are removed before they can be misused unnoticed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>5.3 Disable dormant accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Test procedure</t>
+          <t>Test type</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>List every enabled account. Flag any account that has never signed in, or whose last sign in was 45 days or more before the extraction date, unless an approved exception exists.</t>
+          <t>Operating effectiveness</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Control objective</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>All enabled accounts at the extraction date</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>Accounts nobody uses are removed before they can be misused unnoticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Test procedure</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Whole population</t>
+          <t>List every enabled account. Flag any account that has never signed in, or whose last sign in was 45 days or more before the extraction date, unless an approved exception exists.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Not operating effectively (2 exceptions in 28 tested)</t>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>All enabled accounts at the extraction date</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Whole population</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Not operating effectively (2 exceptions in 28 tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Findings raised</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>F5, F9</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Built in</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Last signed in 2026-10-27.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>adm.akhan</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Last signed in 2026-10-27.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>adm.jcarter</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Built in</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -6327,12 +6797,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>aisha.khan</t>
+          <t>adm.akhan</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -6349,12 +6819,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>ava.king</t>
+          <t>adm.jcarter</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -6371,7 +6841,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ben.foster</t>
+          <t>aisha.khan</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -6393,7 +6863,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>chloe.evans</t>
+          <t>ava.king</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -6415,7 +6885,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>daniel.hughes</t>
+          <t>ben.foster</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -6437,7 +6907,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>emma.wilson</t>
+          <t>chloe.evans</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -6459,7 +6929,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ethan.young</t>
+          <t>daniel.hughes</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6481,12 +6951,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>finance.shared</t>
+          <t>emma.wilson</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -6503,7 +6973,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>grace.thompson</t>
+          <t>ethan.young</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -6525,12 +6995,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>harry.walker</t>
+          <t>finance.shared</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -6547,7 +7017,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>jack.lewis</t>
+          <t>grace.thompson</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -6569,7 +7039,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>james.carter</t>
+          <t>harry.walker</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -6591,7 +7061,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>leo.martin</t>
+          <t>jack.lewis</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -6599,21 +7069,21 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Exception</t>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Never signed in.</t>
+          <t>Last signed in 2026-10-27.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>liam.brooks</t>
+          <t>james.carter</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -6635,7 +7105,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>lucy.hall</t>
+          <t>leo.martin</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -6643,21 +7113,21 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Last signed in 2026-10-27.</t>
+          <t>Never signed in.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>mark.taylor</t>
+          <t>liam.brooks</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -6679,7 +7149,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>mia.roberts</t>
+          <t>lucy.hall</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -6701,7 +7171,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>noah.green</t>
+          <t>mark.taylor</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -6723,7 +7193,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>olivia.bennett</t>
+          <t>mia.roberts</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -6745,7 +7215,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>priya.shah</t>
+          <t>noah.green</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -6767,7 +7237,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ryan.patel</t>
+          <t>olivia.bennett</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -6789,7 +7259,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>sarah.mitchell</t>
+          <t>priya.shah</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -6811,7 +7281,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>sophie.turner</t>
+          <t>ryan.patel</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -6833,12 +7303,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>svc-backup</t>
+          <t>sarah.mitchell</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -6855,35 +7325,81 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>sophie.turner</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Last signed in 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>svc-backup</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Last signed in 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>svc-financeapp</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Never signed in.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:D40"/>
-  <mergeCells count="9">
+  <autoFilter ref="A14:D42"/>
+  <mergeCells count="11">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>

--- a/workpapers/logical-access-workpaper.xlsx
+++ b/workpapers/logical-access-workpaper.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 03:41 UTC</t>
+          <t>2026-10-28 02:11 UTC</t>
         </is>
       </c>
     </row>
